--- a/ED_ItemizedTheory_TieredClaims.xlsx
+++ b/ED_ItemizedTheory_TieredClaims.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core Theory" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core Predictions" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ledger w Claims" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Core Claims" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier Key" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier Counts" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Postulate Flags" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Core Theory" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Core Predictions" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Ledger w Claims" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Core Claims" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Tier Key" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Tier Counts" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Postulate Flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Ratio" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Ledger w Claims'!$A$1:$J$405</definedName>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>a0 = cH0/(2pi) — the MOND transition scale</t>
+          <t>a0 = cH0/(2pi) — the MOND transition scale. **2026-09-04: the 1/(2pi) is NOT established as forced** (Paper_028 §6.3 and Paper_029 §5.1 both evaluate the azimuthal integral to 1, so the factor cancels in their own algebra and is reinstated by a normalization fixed nowhere). Re-tiered Postulated/disputed; gravity Staleness #10. UNAFFECTED: a0 ~ cH0 (reached four independent ways) and a0(z) = cH(z)/(2pi) with exponent 1</t>
         </is>
       </c>
       <c r="D16" s="17" t="inlineStr">
         <is>
-          <t>Constant*</t>
+          <t>Constant* — SCALE ok, COEFFICIENT DISPUTED 2026-09-04</t>
         </is>
       </c>
     </row>
@@ -1535,7 +1535,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="14" customWidth="1" style="39" min="1" max="1"/>
@@ -1615,12 +1615,12 @@
       </c>
       <c r="D3" s="40" t="inlineStr">
         <is>
-          <t>Derived</t>
+          <t>M3 — scale form-derived, COEFFICIENT POSTULATED/DISPUTED (2026-09-04; was 'Derived')</t>
         </is>
       </c>
       <c r="E3" s="40" t="inlineStr">
         <is>
-          <t>a0 tracks H0 wrong as the Hubble tension resolves; wide binaries at a0 obey plain Newton</t>
+          <t>a0 tracks H0 wrong as the Hubble tension resolves [SHARPENED 2026-09-04 as prediction 1.16: inverted, H0 = 2*pi*a0/c gives H0 = 77.0 ± 6.3 km/s/Mpc — +0.62 sigma vs SH0ES, +1.50 sigma vs Planck; needs a0 to ~4% (from ~8%) to arbitrate. This kill-condition already existed qualitatively; 1.16 gives it a number and a precision threshold]; wide binaries at a0 obey plain Newton</t>
         </is>
       </c>
     </row>
@@ -2026,6 +2026,33 @@
       <c r="E18" s="40" t="inlineStr">
         <is>
           <t>resistivity saturation and the viscosity floor onset at different substrate occupancies (no correlation); or a second inter-locus transport channel exists beyond the P05/Adjacency band (F-BAND). Exact ratio needs Pi_p,Pi_q (open); MIR value inherited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="0" t="inlineStr">
+        <is>
+          <t>Gravity</t>
+        </is>
+      </c>
+      <c r="B19" s="0" t="inlineStr">
+        <is>
+          <t>Pred_H0_From_a0</t>
+        </is>
+      </c>
+      <c r="C19" s="0" t="inlineStr">
+        <is>
+          <t>H0 = 2*pi*a0/c — the HUBBLE CONSTANT measured from galaxy rotation curves (ML 1.16, registered 2026-09-04). The inversion of a0 = cH0/(2pi). NO MOND ANALOGUE: there a0 is a constant of nature with no cosmological connection, so there is nothing to invert. Current value: 77.0 ± 6.3 km/s/Mpc from Desmond 2023 — +0.62 sigma vs SH0ES, +1.50 sigma vs Planck. Systematics (stellar M/L) uncorrelated with both the CMB sound horizon and the distance ladder.</t>
+        </is>
+      </c>
+      <c r="D19" s="0" t="inlineStr">
+        <is>
+          <t>M3 — CONDITIONAL on the disputed 2pi; a test of that coefficient, never evidence for it</t>
+        </is>
+      </c>
+      <c r="E19" s="0" t="inlineStr">
+        <is>
+          <t>F1: if a0 tightens to ±0.05e-10 and the CMB H0 holds, the implied H0 sits ~3 sigma off and the 2pi is refuted BY MEASUREMENT with no derivation attempted. F2: a local-ladder H0 with a0 near 1.13e-10 confirms it below 1 sigma. F3: if the ML 1.15 exponent test fails, horizon-tying fails and this goes with it. Needs a0 to ~4% (from ~8%) for ±3 km/s/Mpc. Registered BEFORE that precision exists, so a later agreement is a prediction and not a postdiction.</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2825,7 @@
       </c>
       <c r="D20" s="41" t="inlineStr">
         <is>
-          <t>Constant</t>
+          <t>Constant (scale) / POSTULATED-DISPUTED (coefficient) — 2026-09-04</t>
         </is>
       </c>
       <c r="E20" s="41" t="n"/>
@@ -2810,7 +2837,7 @@
       </c>
       <c r="H20" s="41" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>STALE AS OF 2026-09-04 — was 'current'. The 1/(2pi) is re-tiered **Postulated/disputed** (gravity Staleness #10): it cancels in Paper_028 §6.3 / Paper_029 §5.1's own displayed algebra. The SCALE a0 ~ cH0 stands and is now reached FOUR independent ways (dipole projection; Rindler/de Sitter smoothness; horizon-competition threshold #34; content-depth #38) — none reaches the coefficient. Empirical standing tightened 2026-09-04: Desmond 2023 (a0 = 1.19 ± 0.04 ± 0.09) puts the 2pi at 1.09 sigma (was 0.49 sigma vs the 2016 systematic), and it PREFERS A HIGH H0 — 1.50 sigma vs Planck, 0.62 sigma vs SH0ES. See Paper_029 §5.5, Staleness #39</t>
         </is>
       </c>
       <c r="I20" s="41" t="n"/>
@@ -4478,7 +4505,7 @@
       </c>
       <c r="H61" s="41" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current — STRENGTHENED 2026-09-04 (gravity Staleness #37). Paper_030 §5.3 previously reached the deep-MOND branch via an explicit REGIME ASSUMPTION (that the bilocal cross-term dominates two pure-source terms), which was false as stated and load-bearing. Sigma_0 is now a content normalization, no gradient is taken, the profile is a = a_N + sqrt(a_N a0), and **a -&gt; sqrt(a_N a0) follows as a LIMIT, not an assumption**. Verified numerically over a_N/a0 = 1e6..1e-6. Derived tier better supported than when this row was written. NOTE the mu form is now filed INHERITED (it is the V5 envelope shape, Paper_090 §7.2 value-layer; Staleness #34), not open</t>
         </is>
       </c>
       <c r="I61" s="41" t="n"/>
@@ -9042,7 +9069,7 @@
       </c>
       <c r="H172" s="41" t="inlineStr">
         <is>
-          <t>current — RESOLVED, near-term weapon closed (consistency result). BODY stale vs its own banner (Staleness #1)</t>
+          <t>current — RESOLVED, near-term weapon closed (consistency result). [CORRECTED 2026-09-04: the banner/body desync was FIXED 2026-07-29 (the paper reads 'Status: RESOLVED' with a pre-resolution note ahead of the 2026-07-21 EFE calculation). What was stale was the ARC-STATE PROSE still listing it as a live exception, corrected 2026-09-04 — gravity Staleness #32. Fourth instance of a staleness note that is itself stale.] superseded text: BODY stale vs its own banner (Staleness #1)</t>
         </is>
       </c>
       <c r="I172" s="41" t="inlineStr">
@@ -16421,7 +16448,7 @@
       </c>
       <c r="C362" s="41" t="inlineStr">
         <is>
-          <t>MOND = the off-diagonal HORIZON-INTERFERENCE cross-term; sqrt(a_N a0) forced</t>
+          <t>MOND = the off-diagonal HORIZON-INTERFERENCE cross-term; sqrt(a_N a0) forced GIVEN P14 + the bilocal-channel construction (scoped 2026-09-04)</t>
         </is>
       </c>
       <c r="D362" s="41" t="inlineStr">
@@ -16442,7 +16469,7 @@
       </c>
       <c r="H362" s="41" t="inlineStr">
         <is>
-          <t>current</t>
+          <t>current — re-checked 2026-09-04 (Staleness #37). The cross-term SURVIVED the Sigma_0 rewrite: Paper_030 §4.2 uses a0*R as a per-channel CONTENT measure (legitimate; = c^2/2pi at the horizon), whereas §3.2 took its GRADIENT and called it a force (removed). Same expression, two uses, one licensed. 'Forced' scoped to P14 per the strength-word rule (checklist item 20c)</t>
         </is>
       </c>
       <c r="I362" s="41" t="inlineStr">
@@ -19102,12 +19129,12 @@
       </c>
       <c r="C17" s="17" t="inlineStr">
         <is>
-          <t>a0 = cH0/(2pi) — the MOND transition scale</t>
+          <t>a0 = cH0/(2pi) — the MOND transition scale. **2026-09-04: the 1/(2pi) is NOT established as forced** — it cancels in Paper_028 §6.3 / Paper_029 §5.1's own displayed algebra and is reinstated by a normalization fixed nowhere. Re-tiered Postulated/disputed (gravity Staleness #10). UNAFFECTED: a0 ~ cH0, now reached FOUR independent ways, and a0(z) = cH(z)/(2pi) exponent 1</t>
         </is>
       </c>
       <c r="D17" s="20" t="inlineStr">
         <is>
-          <t>Constant*</t>
+          <t>Constant* — SCALE ok, COEFFICIENT DISPUTED 2026-09-04</t>
         </is>
       </c>
     </row>
@@ -19815,7 +19842,7 @@
       </c>
       <c r="C49" s="32" t="inlineStr">
         <is>
-          <t>Hawking temperature T_H = kappa/2pi via V5 KMS</t>
+          <t>Hawking temperature T_H = kappa/2pi via V5 KMS. [2026-09-04: this 2pi is NOT the disputed one. It comes from near-horizon Euclidean smoothness (no conical defect) in Paper_BH_Thermal2Pi and does not cancel. The a0 dispute (row 17) is about the azimuthal-Fourier factor in Paper_029. Whether they are the SAME 2pi is exactly Route 2 of research target #18, and is open]</t>
         </is>
       </c>
       <c r="D49" s="32" t="inlineStr">
@@ -24694,7 +24721,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="65.86" customWidth="1" style="39" min="3" max="3"/>
@@ -24781,6 +24808,18 @@
       <c r="C7" s="33" t="inlineStr">
         <is>
           <t>Foundations rows about the axiom system, not per-domain knobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="0" t="inlineStr">
+        <is>
+          <t>SCOPE NOTE — added 2026-09-04</t>
+        </is>
+      </c>
+      <c r="C9" s="0" t="inlineStr">
+        <is>
+          <t>These flags describe the 24 Postulated-tier CLAIM ROWS in this workbook, not the corpus's postulate inventory. A mechanical census on 2026-09-04 found 173 distinctly-named P-* postulates in physics-papers/. Both figures are correct on their own basis; neither should be quoted without it. See the Ratio sheet's basis note and research target #20.</t>
         </is>
       </c>
     </row>
@@ -24798,7 +24837,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="45.14" customWidth="1" style="39" min="1" max="1"/>
@@ -24927,6 +24966,64 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="0" t="inlineStr">
+        <is>
+          <t>BASIS NOTE — added 2026-09-04</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="0" t="inlineStr">
+        <is>
+          <t>What '15 live' counts</t>
+        </is>
+      </c>
+      <c r="B12" s="0" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="C12" s="0" t="inlineStr">
+        <is>
+          <t>Claim ROWS in this workbook tiered 'Postulated' whose postulate is still live (Claims col J) — NOT a census of named postulates in the corpus. Stating it as 'the only genuinely per-domain knobs' without this basis understates the declared assumption load as a reader would measure it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="0" t="inlineStr">
+        <is>
+          <t>Mechanical census, same date</t>
+        </is>
+      </c>
+      <c r="B13" s="0" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="C13" s="0" t="inlineStr">
+        <is>
+          <t>Distinctly-named P-* postulates across physics-papers/ (7 further matches merged as spelling variants), so the declared set is 13 primitives + 173 = 186. Re-runnable: internal notes/_census_postulates.py, which exits nonzero when the count drifts from its baseline. Paper_088 stated 31 and Paper_087 §4.15 ~35; both now carry dated census notes. Paper_100's '60+' is the least wrong figure in the corpus.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="0" t="inlineStr">
+        <is>
+          <t>Which number belongs in the ratio</t>
+        </is>
+      </c>
+      <c r="B14" s="0" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C14" s="0" t="inlineStr">
+        <is>
+          <t>Research target #20 (event-density/docs/ED_Research_Targets.md): whether all 173 are load-bearing postulates or whether most are local modelling choices that should not count against parsimony. Until that is settled the figure of merit should quote BOTH numbers with their bases, not 15 alone. Gravity Staleness #33.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>

--- a/ED_ItemizedTheory_TieredClaims.xlsx
+++ b/ED_ItemizedTheory_TieredClaims.xlsx
@@ -24837,7 +24837,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="45.14" customWidth="1" style="39" min="1" max="1"/>
@@ -25024,6 +25024,121 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BASIS LADDER — resolved 2026-09-04 (research target #20 CLOSED)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Full working: internal notes/POSTULATE_BASIS.md. Re-derive: _census_postulates.py --triage</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>declared anywhere</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>171</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>+13 primitives = 184. Every named commitment in physics-papers/, incl. one-off modelling choices</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>used in &gt;=2 papers</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>68</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>+13 = 81. The commitment outlives the derivation that introduced it</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>used in &gt;=3 papers</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>43</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>+13 = 56</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CROSS-CUTTING, &gt;=4 papers</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>26</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>+13 = 39. The framework's standing commitments. This is the row to quote for parsimony</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>carries a Postulated-tier claim row</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>14</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>+13 = 27. THIS workbook's basis — the 'live' flag in Claims col J</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>used in exactly ONE paper</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>103</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>60% of the total. Local modelling choices, scoped to a single derivation, like a gauge choice</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>RECOMMENDATION</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Quote the LADDER, not a number. Both the honest large figure (171) and the honest small one (26) belong in public material; either alone misleads.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:C1"/>

--- a/ED_ItemizedTheory_TieredClaims.xlsx
+++ b/ED_ItemizedTheory_TieredClaims.xlsx
@@ -679,7 +679,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="14.43" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="25" customWidth="1" style="39" min="1" max="1"/>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="C24" s="21" t="inlineStr">
         <is>
-          <t>a0 &amp; xi_canonical FORCED to share one substrate-cosmology boundary origin</t>
+          <t>a0 &amp; xi_canonical FORCED to share one substrate-cosmology boundary origin. **CHECKED 2026-09-04 against the a0 work — line SURVIVES, and is if anything strengthened.** What the two scales are claimed to share is the boundary object $R_H = c/H_0$, **not** the coefficient. The 1/(2pi) is now disputed (row 16, gravity Staleness #10) and that dispute does **not** reach this line: the coefficient sits on a0, the shared origin sits on R_H. Meanwhile a0 ~ cH0 gained a FOURTH independent route the same day (horizon-competition threshold, Staleness #34), so the horizon-tying half of the pair is better supported than when this row was written. **Tier 'Postulated' is correct and unchanged** — it rests on the named postulate P-Substrate-Cosmology-Unified (SCBU), and the paper's own verdict is M3 form-FORCED + value-INHERITED. **Two residuals worth carrying, neither a tier change:** (i) the OTHER half of the pair, xi_canonical = 1.7575 lu, is **canon-INTERNAL and sourced to MEMORY FILES rather than a paper** (Foundations ledger staleness #4) — the corpus's own read-first rule denies memory authority, so half this claim rests on the pointer layer; (ii) SCBU's step 12 leaves the functional form of xi_canonical(H0) **OPEN**, so what is claimed is co-variation under H0, not a derived relation. 'FORCED' is defensible *given the postulate* and should not be read as unconditional.</t>
         </is>
       </c>
       <c r="D24" s="21" t="inlineStr">
@@ -1521,6 +1521,54 @@
       <c r="D38" s="21" t="inlineStr">
         <is>
           <t>Postulated</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>WHAT THE 38 LINES ARE — basis stated 2026-09-04</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>13 primitives (rows 1-13) + 10 constants (14-23) + 15 postulates (24-38) = 38. **This is ED's structural SPINE, not its full assumption list.** The 15 postulates here are the ones attached to HEADLINE claims, which is a narrower basis than either of the two natural alternatives.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>The ladder, for comparison</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Postulates used in &gt;=4 papers (cross-cutting): 26. Declared anywhere in physics-papers/: 171. So a reader who takes '38 lines' as 'everything ED assumes' is understating the declared load by an order of magnitude — the same exposure Paper_088's '31 total' carried before it was re-scoped (gravity Staleness #33). Read as 'the spine', the figure is accurate and it is a good frame. The difference is this sentence.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Selection is by headline, not by load</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>The 15 here overlap only partly with the 26 cross-cutting ones. In both: P-RB-1, P-Quadratic-Strain, P-Profile-Rescaling, P-QD-LiveWeight. Heavily used across the corpus but NOT among the 38: P-Codim-1 (10 papers), P-Corr-Budget (10), P-LinRate (9), P-Channel-Orthogonality (7), P-Sat (7). So these 15 are 'the postulates carrying headline claims', not 'the most load-bearing postulates'. Both are legitimate selections; only one is what the row set actually is.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Full working</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>internal notes/POSTULATE_BASIS.md (research target #20, CLOSED 2026-09-04). Re-derive: _census_postulates.py --triage</t>
         </is>
       </c>
     </row>
@@ -19305,7 +19353,7 @@
       </c>
       <c r="C25" s="21" t="inlineStr">
         <is>
-          <t>a0 &amp; xi_canonical FORCED to share one substrate-cosmology boundary origin</t>
+          <t>a0 &amp; xi_canonical FORCED to share one substrate-cosmology boundary origin. **CHECKED 2026-09-04: survives — the shared object is R_H, not the coefficient; the 1/(2pi) dispute does not reach it, and a0 ~ cH0 gained a fourth route the same day. Tier unchanged. Residuals: xi_canonical is canon-INTERNAL and memory-sourced (Foundations staleness #4), and SCBU step 12 leaves xi_canonical(H0) OPEN — so 'FORCED' is conditional on P-Substrate-Cosmology-Unified. See Core Theory row 24.**</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -25025,115 +25073,115 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="0" t="inlineStr">
         <is>
           <t>BASIS LADDER — resolved 2026-09-04 (research target #20 CLOSED)</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="0" t="inlineStr">
         <is>
           <t>Full working: internal notes/POSTULATE_BASIS.md. Re-derive: _census_postulates.py --triage</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="0" t="inlineStr">
         <is>
           <t>declared anywhere</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" s="0" t="n">
         <v>171</v>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="0" t="inlineStr">
         <is>
           <t>+13 primitives = 184. Every named commitment in physics-papers/, incl. one-off modelling choices</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="0" t="inlineStr">
         <is>
           <t>used in &gt;=2 papers</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" s="0" t="n">
         <v>68</v>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="0" t="inlineStr">
         <is>
           <t>+13 = 81. The commitment outlives the derivation that introduced it</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="0" t="inlineStr">
         <is>
           <t>used in &gt;=3 papers</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" s="0" t="n">
         <v>43</v>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="0" t="inlineStr">
         <is>
           <t>+13 = 56</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="0" t="inlineStr">
         <is>
           <t>CROSS-CUTTING, &gt;=4 papers</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" s="0" t="n">
         <v>26</v>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="0" t="inlineStr">
         <is>
           <t>+13 = 39. The framework's standing commitments. This is the row to quote for parsimony</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="0" t="inlineStr">
         <is>
           <t>carries a Postulated-tier claim row</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="0" t="inlineStr">
         <is>
           <t>+13 = 27. THIS workbook's basis — the 'live' flag in Claims col J</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="0" t="inlineStr">
         <is>
           <t>used in exactly ONE paper</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" s="0" t="n">
         <v>103</v>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="0" t="inlineStr">
         <is>
           <t>60% of the total. Local modelling choices, scoped to a single derivation, like a gauge choice</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="0" t="inlineStr">
         <is>
           <t>RECOMMENDATION</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
+      <c r="B23" s="0" t="inlineStr"/>
+      <c r="C23" s="0" t="inlineStr">
         <is>
           <t>Quote the LADDER, not a number. Both the honest large figure (171) and the honest small one (26) belong in public material; either alone misleads.</t>
         </is>

--- a/ED_ItemizedTheory_TieredClaims.xlsx
+++ b/ED_ItemizedTheory_TieredClaims.xlsx
@@ -1525,48 +1525,48 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="0" t="inlineStr">
         <is>
           <t>WHAT THE 38 LINES ARE — basis stated 2026-09-04</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="0" t="inlineStr">
         <is>
           <t>13 primitives (rows 1-13) + 10 constants (14-23) + 15 postulates (24-38) = 38. **This is ED's structural SPINE, not its full assumption list.** The 15 postulates here are the ones attached to HEADLINE claims, which is a narrower basis than either of the two natural alternatives.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="0" t="inlineStr">
         <is>
           <t>The ladder, for comparison</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="0" t="inlineStr">
         <is>
           <t>Postulates used in &gt;=4 papers (cross-cutting): 26. Declared anywhere in physics-papers/: 171. So a reader who takes '38 lines' as 'everything ED assumes' is understating the declared load by an order of magnitude — the same exposure Paper_088's '31 total' carried before it was re-scoped (gravity Staleness #33). Read as 'the spine', the figure is accurate and it is a good frame. The difference is this sentence.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="0" t="inlineStr">
         <is>
           <t>Selection is by headline, not by load</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="0" t="inlineStr">
         <is>
           <t>The 15 here overlap only partly with the 26 cross-cutting ones. In both: P-RB-1, P-Quadratic-Strain, P-Profile-Rescaling, P-QD-LiveWeight. Heavily used across the corpus but NOT among the 38: P-Codim-1 (10 papers), P-Corr-Budget (10), P-LinRate (9), P-Channel-Orthogonality (7), P-Sat (7). So these 15 are 'the postulates carrying headline claims', not 'the most load-bearing postulates'. Both are legitimate selections; only one is what the row set actually is.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="0" t="inlineStr">
         <is>
           <t>Full working</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="0" t="inlineStr">
         <is>
           <t>internal notes/POSTULATE_BASIS.md (research target #20, CLOSED 2026-09-04). Re-derive: _census_postulates.py --triage</t>
         </is>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="C19" s="0" t="inlineStr">
         <is>
-          <t>H0 = 2*pi*a0/c — the HUBBLE CONSTANT measured from galaxy rotation curves (ML 1.16, registered 2026-09-04). The inversion of a0 = cH0/(2pi). NO MOND ANALOGUE: there a0 is a constant of nature with no cosmological connection, so there is nothing to invert. Current value: 77.0 ± 6.3 km/s/Mpc from Desmond 2023 — +0.62 sigma vs SH0ES, +1.50 sigma vs Planck. Systematics (stellar M/L) uncorrelated with both the CMB sound horizon and the distance ladder.</t>
+          <t>H0 = 2*pi*a0/c - the HUBBLE CONSTANT measured from galaxy rotation curves (ML 1.16, registered 2026-09-04). The inversion of a0 = cH0/(2pi). CORRECTED 2026-09-05: this entry previously read 'NO MOND ANALOGUE: there a0 is a constant of nature with no cosmological connection.' That was wrong. The a0-cosmology connection is standard MOND material - Milgrom (2020), arXiv:2001.09729, is a review devoted to it, and the 2pi-normalized form a0 = cH0/(2pi) is itself quoted in the MOND review literature (Famaey &amp; McGaugh 2012). WHAT MOND LACKS IS A DERIVED COEFFICIENT: an order-of-magnitude relation inverts only to an order-of-magnitude H0, which measures nothing. ED's novelty here is the normalization, not the connection - so this probe's entire distinctiveness rests on the 2pi, which is itself Postulated/disputed. Current value: 77.0 +/- 6.3 km/s/Mpc from Desmond 2023 - +0.62 sigma vs SH0ES, +1.50 sigma vs Planck. Systematics (stellar M/L) uncorrelated with both the CMB sound horizon and the distance ladder.</t>
         </is>
       </c>
       <c r="D19" s="0" t="inlineStr">
